--- a/venv/Google map/Chợ/new_address_result (4).xlsx
+++ b/venv/Google map/Chợ/new_address_result (4).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin Data\PycharmProjects\pythonProject1\github\Code_python\venv\Google map\Chợ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9280C7FD-32BE-4BBE-BF16-6F040C7C370D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36145D5-8D44-46E0-8725-12EF92AB6D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,15 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="91">
   <si>
-    <t>Tên Chợ</t>
-  </si>
-  <si>
-    <t>Oldaddress</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
     <t>website</t>
   </si>
   <si>
@@ -293,6 +284,15 @@
   </si>
   <si>
     <t>cho</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>OldAddress</t>
   </si>
 </sst>
 </file>
@@ -364,7 +364,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -681,42 +681,42 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>16.493593700000002</v>
@@ -725,27 +725,27 @@
         <v>107.58181190000001</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
       </c>
       <c r="D3">
         <v>84702187321</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>16.454831500000001</v>
@@ -754,21 +754,21 @@
         <v>107.5923026</v>
       </c>
       <c r="H3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>16.559702300000001</v>
@@ -777,21 +777,21 @@
         <v>107.55474769999999</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>16.463711700000001</v>
@@ -800,21 +800,21 @@
         <v>107.5908628</v>
       </c>
       <c r="H5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>84978930807</v>
@@ -826,27 +826,27 @@
         <v>106.7098293</v>
       </c>
       <c r="H6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
       </c>
       <c r="D7">
         <v>84978953953</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>16.466918</v>
@@ -855,27 +855,27 @@
         <v>107.5822994</v>
       </c>
       <c r="H7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
       </c>
       <c r="D8">
         <v>84825634234</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>16.463743900000001</v>
@@ -884,21 +884,21 @@
         <v>107.59265190000001</v>
       </c>
       <c r="H8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>16.463711700000001</v>
@@ -907,27 +907,27 @@
         <v>107.5908628</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
         <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
       </c>
       <c r="D10">
         <v>84386867123</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>16.037223000000001</v>
@@ -936,21 +936,21 @@
         <v>108.2245568</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>84338497356</v>
@@ -962,21 +962,21 @@
         <v>105.7599886</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F12">
         <v>20.979841499999999</v>
@@ -985,21 +985,21 @@
         <v>105.7668802</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>20.727684799999999</v>
@@ -1008,21 +1008,21 @@
         <v>107.0463682</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F14">
         <v>10.766526900000001</v>
@@ -1031,24 +1031,24 @@
         <v>106.69796479999999</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
         <v>48</v>
       </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F15">
         <v>10.737394200000001</v>
@@ -1057,27 +1057,27 @@
         <v>106.7295721</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
         <v>52</v>
-      </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
       </c>
       <c r="D16">
         <v>84901868786</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F16">
         <v>10.7283553</v>
@@ -1086,27 +1086,27 @@
         <v>106.74438290000001</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
         <v>56</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>59</v>
       </c>
       <c r="D17">
         <v>84948608686</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F17">
         <v>10.736074199999999</v>
@@ -1115,27 +1115,27 @@
         <v>106.7212988</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
         <v>60</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>63</v>
       </c>
       <c r="D18">
         <v>84901262830</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F18">
         <v>10.7773167</v>
@@ -1144,21 +1144,21 @@
         <v>106.6977562</v>
       </c>
       <c r="H18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F19">
         <v>20.963975999999999</v>
@@ -1167,21 +1167,21 @@
         <v>105.780891</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F20">
         <v>16.4788143</v>
@@ -1190,24 +1190,24 @@
         <v>107.5824073</v>
       </c>
       <c r="H20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
         <v>70</v>
       </c>
-      <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F21">
         <v>16.466961000000001</v>
@@ -1216,21 +1216,21 @@
         <v>107.5890376</v>
       </c>
       <c r="H21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I21" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F22">
         <v>21.026558000000001</v>
@@ -1239,21 +1239,21 @@
         <v>105.839181</v>
       </c>
       <c r="H22" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D23">
         <v>84706598530</v>
@@ -1265,21 +1265,21 @@
         <v>106.65746230000001</v>
       </c>
       <c r="H23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F24">
         <v>10.755114799999999</v>
@@ -1288,21 +1288,21 @@
         <v>106.65492039999999</v>
       </c>
       <c r="H24" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D25">
         <v>84816667955</v>
@@ -1314,10 +1314,10 @@
         <v>106.6610426</v>
       </c>
       <c r="H25" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
